--- a/结果/实盘成交明细_脱敏.xlsx
+++ b/结果/实盘成交明细_脱敏.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'成交明细'!$A$1:$H$1364</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'配对明细'!$A$1:$H$649</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'汇总'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'汇总'!$A$1:$B$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'月度统计'!$A$1:$H$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63643,10 +63643,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -63765,7 +63765,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>已实现净盈亏</t>
+          <t>程序配对已实现盈亏（仅供参考）</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -63785,45 +63785,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>期初现金估算</t>
+          <t>东方财富净盈亏（含费用）</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21460.15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>银证净转入</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-32884.09000000013</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>期末总资产</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>34002.49</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>账户总盈亏估算</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>45426.43000000012</v>
+        <v>66886.58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B17"/>
+  <autoFilter ref="A1:B14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
